--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>0</v>
